--- a/data/daily/2026-09/2026-09-25.xlsx
+++ b/data/daily/2026-09/2026-09-25.xlsx
@@ -1245,57 +1245,57 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1500,57 +1500,57 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1780,14 +1780,39 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="457200" cy="438150"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="457200" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1802,17 +1827,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="457200" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1827,35 +1852,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="457200" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="457200" cy="361950"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -2035,27 +2035,52 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1238250" cy="1190625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -2063,54 +2088,29 @@
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="990600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -2600,22 +2600,18 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>뛰어난 피로 회복 효과 — 섭취 후 피로 회복 및 활력 증진에 도움을 줌</t>
+          <t>뛰어난 피로회복 — 섭취 후 몸의 피로 회복과 활력 보충에 탁월한 효과를 느낌.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>만족도 높은 선물 구성 — 받았을 때 기분이 좋고 주변과 나눠 먹기 좋은 선물임</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>섭취 및 배송 편의성 — 마시기 편하고 배송 속도가 빠른 편임</t>
-        </is>
-      </c>
+          <t>만족스러운 선물 — 가성비는 낮지만 주고받을 때 서로 기분이 좋아져 선물용으로 매우 유용함.</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>높은 가격 부담 — 영양제 가격대가 다소 비싸 부담스러움</t>
+          <t>부담스러운 가격 — 영양제의 효능은 만족스러우나 타 제품 대비 가격이 꽤 비싼 편임.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -2663,17 +2659,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>활력 및 피로 개선 — 섭취 시 활력이 도는 느낌을 받으며 피로 해소에 도움 됨</t>
+          <t>활력 증진 효과 — 피곤할 때 섭취하면 몸에 빠르게 활력이 도는 느낌을 받음.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>고급스러운 선물 포장 — 포장이 고급스럽고 추가 증정 및 메시지 카드가 동봉되어 만족스러움</t>
+          <t>고급스러운 포장 — 패키지가 고급스럽고 메시지 카드가 동봉되어 선물용으로 탁월함.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>빠른 배송 및 편의성 — 먹기 편하며 추석 연휴 전 빠르게 배송됨</t>
+          <t>편안한 섭취 방법 — 먹기에 부담이 없고 영양 성분 구성이 훌륭하여 챙겨 먹기 수월함.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2722,22 +2718,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>피로 감소 및 활력 증진 — 체력적으로 힘든 일할 때 마시면 생기와 활력이 느껴짐</t>
+          <t>뛰어난 피로개선 — 고된 노동이나 활동 후 마시면 생기와 컨디션 회복에 큰 도움이 됨.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>선물용 만족도 — 지인이나 가족에게 선물했을 때 기쁨과 만족도가 큼</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>할인 쿠폰 구매 혜택 — 할인 쿠폰을 적용하여 좋은 가격에 구매 가능함</t>
-        </is>
-      </c>
+          <t>선물용으로 추천 — 가족이나 지인에게 기분 좋게 마음을 전할 수 있는 정답 같은 선물임.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>쇼핑백 품질 불량 — 함께 전달된 쇼핑백 상태가 불량하여 선물하기 아쉬움</t>
+          <t>쇼핑백 품질 불량 — 함께 동봉된 선물용 백의 마감이나 상태가 불량하여 사용하기 어려웠음.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -2785,22 +2777,18 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>활력 및 피로 회복 — 마시면 힘이 나고 피로할 때 도움을 줌</t>
+          <t>간편한 개별포장 — 한 포씩 개별 포장되어 사무실 책상이나 가방에 휴대하여 먹기 편함.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>개별 포장 및 휴대 편의성 — 한 포씩 개별 포장되어 가방이나 책상에 두고 챙겨 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>빠른 배송과 저렴한 가격 — 배송이 빠르고 저렴한 가격으로 구매할 수 있음</t>
-        </is>
-      </c>
+          <t>우수한 피로회복 — 피로가 누적되었을 때 섭취하면 빠르게 힘이 나는 느낌을 줌.</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>배송 요청사항 미반영 — 관리실 위탁 요청에도 불구하고 문 앞에 두고 간 점이 아쉬움</t>
+          <t>배송 요청 미준수 — 부재 시 경비실 위탁을 사전 요청했으나 문 앞에 두고 가 아쉬웠음.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -2844,21 +2832,21 @@
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>피로 개선 및 활력 충전 — 피곤할 때 섭취하기 좋고 활력이 상승하는 느낌을 줌</t>
+          <t>선물하기 좋은 구성 — 쇼핑백이 기본 동봉되고 포장이 정성스러워 선물용으로 안성맞춤임.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>선물하기 좋은 구성 — 포장이 깔끔하고 쇼핑백이 함께 들어있어 선물용으로 적합함</t>
+          <t>휴대 및 섭취 용이 — 한 병씩 개별 용기로 되어 있어 여행 시 들고 다니며 챙겨 먹기 유용함.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>넉넉한 용량과 높은 휴대성 — 양해 넉넉하고 여행 시 들고 다니며 챙겨 먹기 용이함</t>
+          <t>확실한 컨디션 개선 — 피로할 때 섭취 시 활력이 생겨 건강이 증진되는 효과를 직접 경험함.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -2907,22 +2895,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>뛰어난 맛과 피로 회복 — 맛있고 피로가 빠르게 풀리는 효과를 기대할 수 있음</t>
+          <t>맛있는 액상형 — 영양제임에도 맛있게 복용할 수 있고 피로 해소가 빠른 편임.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>고급스러운 포장 디자인 — 패키지가 고급스럽고 예쁘게 잘 되어 있어 선물하기 좋음</t>
+          <t>고급스러운 패키지 — 대기업 브랜드 제품답게 포장이 고급스러워 신뢰도 높은 선물로 제격임.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>개별 포장의 편의성 — 간편하게 개별 포장되어 있어 들고 다니며 먹기 편함</t>
+          <t>편리한 개별포장 — 직장 등에서 간편하게 휴대하며 한 병씩 꺼내 먹기 용이함.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>야간 섭취 시 수면 방해 — 저녁 늦게 섭취 시 활력 성분으로 인해 잠들기 어려울 수 있음</t>
+          <t>수면 방해 가능성 — 피로회복 성분이 강하여 늦은 저녁에 복용 시 수면에 방해가 될 수 있음.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -2970,23 +2958,23 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>피로 회복 및 높은 섭취 편의성 — 피로감이 줄어들고 캡슐과 액상을 한 번에 먹기 편함</t>
+          <t>옵션 선택 다양성 — 옵션에서 취향에 맞는 맛이나 성분을 직접 고를 수 있어 만족스러움.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>알찬 구성 및 합리적 가격 — 30일 분량의 합리적인 가격대와 유용한 옵션 구성을 제공함</t>
+          <t>정성스러운 포장 — 패키징이 매우 신경 써서 준비된 느낌을 주어 받는 사람의 기분이 좋아짐.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>배송 포장 오염 및 먼지 — 쇼핑백과 제품 박스 표면에 먼지 및 이물질이 가득 묻어옴</t>
+          <t>비위생적 제품 상태 — 택배 상자 내부에 먼지나 이물질이 가득 묻은 상태로 배송되어 불쾌함.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>개봉 씰 훼손 및 재부착 흔적 — 밀봉 스티커가 떼어져 있거나 재부착된 흔적이 있어 선물 시 찝찝함</t>
+          <t>스티커 훼손 의심 — 박스 밀봉용 실 스티커가 반쯤 떨어져 있거나 재부착 흔적이 남아 찝찝함.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -3029,21 +3017,21 @@
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>8723</v>
+        <v>8724</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>에너지 충전 및 피로 개선 — 꾸준히 마시면 힘이 나고 피로가 해소되는 느낌을 받음</t>
+          <t>뛰어난 활력 증진 — 점심이나 힘든 일과 중 복용하면 즉각적으로 몸에 기운이 쌩쌩하게 돎.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>상큼한 오렌지 맛 — 거부감 없이 맛있게 먹을 수 있는 오렌지 맛임</t>
+          <t>맛있는 오렌지맛 — 비타민 특유의 거부감 없이 맛있는 오렌지 맛으로 수월하게 먹을 수 있음.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>예쁘고 정성스러운 포장 — 패키지가 예쁘고 꼼꼼하게 포장되어 전달됨</t>
+          <t>예쁜 패키지 포장 — 꼼꼼하고 화사하게 잘 포장되어 선물용으로 매우 만족스러움.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -3092,22 +3080,18 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>성별 맞춤 영양 설계 — 성별에 맞춰 선택할 수 있고 영양소 함량이 높음</t>
+          <t>맞춤형 옵션 선택 — 성별(m/f)에 맞춤 설계된 제품 옵션을 선택하여 선물할 수 있어 유용함.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>지속적인 효과 및 피로 개선 — 꾸준히 먹으면 덜 피곤하고 활력이 지속되는 효과를 느낌</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>정성스러운 선물 포장 — 선물 느낌이 가득한 포장으로 전달받았을 때 만족도가 높음</t>
-        </is>
-      </c>
+          <t>우수한 피로 개선 — 섭취 후 오랜 시간 피로감이 줄고 반짝이는 활력 효과가 오래 유지됨.</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>다소 큰 알약 크기 — 기존 제품 대비 알약 크기가 커서 삼키기 다소 힘듦</t>
+          <t>큰 알약 크기 — 동봉된 알약의 크기가 기존 제품보다 큰 편이라 삼키는 데 다소 부담스러움.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -3155,19 +3139,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>맛있는 구미 형태 — 마이구미처럼 맛있어 영양제라는 부담 없이 먹기 좋음</t>
+          <t>편리한 섭취 방식 — 물 없이도 출근길이나 야외에서 젤리처럼 가볍게 씹어서 먹을 수 있음.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>물 없이 먹는 편의성 — 젤리 제형이라 물 없이 간편하게 챙겨 먹기 유용함</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>귀엽고 깔끔한 패키지 — 포장이 귀엽고 깔끔해 가볍게 선물하기 적합함</t>
-        </is>
-      </c>
+          <t>맛있는 구미 제형 — 영양제 냄새 없이 맛있는 마이구미 젤리 같아 남녀노소 즐기기 좋음.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -3214,22 +3194,22 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>고급스러운 보자기 포장 — 보자기, 틴케이스 등 선물용으로 완성도 높은 포장을 제공함</t>
+          <t>품격 있는 포장 — 오간자, 보자기, 고급 틴케이스 등 정성 가득하고 정밀한 패키지가 아름다움.</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>비리지 않고 뛰어난 맛 — 비린 맛이 전혀 없고 새콤하고 맛있게 섭취 가능함</t>
+          <t>비리지 않은 맛 — 콜라겐 특유의 텁텁하고 비린 맛이 느껴지지 않아 편하게 복용 가능함.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>낱개 앰플의 간편함 — 낱개로 포장되어 하나씩 개봉해 먹기 편함</t>
+          <t>간편한 앰플 형태 — 개별 앰플 제형으로 포장을 따서 즉시 마실 수 있어 관리가 간편함.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>다소 높은 가격 부담 — 가격대가 다소 비싸고 점점 상승하는 경향이 있음</t>
+          <t>높은 가격대 — 원료가 좋으나 가격대가 제법 비싼 편이며 점차 가격이 올라 부담됨.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -3277,27 +3257,31 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>속 편한 소화 개선 효과 — 식후 섭취 시 소화가 잘 되고 속 불편함이 해소됨</t>
+          <t>뛰어난 소화 효과 — 식후에 섭취 시 속 더부룩함이 가라앉고 속이 매우 편안해짐.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>고소하고 부담 없는 맛 — 고소한 맛이 나며 거부감 없이 맛있게 섭취 가능함</t>
+          <t>거부감 없는 맛 — 고소하고 군고구마 같은 맛이 나서 거부감 없이 쉽게 삼키기 좋음.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>풍성한 사은품과 합리적 가격 — 단백질 바 등 사은품 혜택이 좋고 가격 대비 구성이 알참</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>풍성한 혜택 구성 — 라이브 방송 혜택 등으로 사은품과 증정품을 풍성하게 제공받음.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>아쉬운 증정품 크기 — 함께 사은품으로 딸려 온 단백질칩 등의 사이즈가 매우 작아 실망스러움.</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
     <row r="14" ht="38" customHeight="1">
       <c r="B14" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3305,58 +3289,54 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>64,200원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260911094744_fdcb15f83b684390b6fd43416e90d400.jpg</t>
         </is>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>56</v>
+        <v>898</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>부드러운 식감과 다양한 맛 — 닭가슴살이 부드럽고 질리지 않는 다양한 맛으로 구성됨</t>
+          <t>우수한 가성비 — 합리적이고 저렴한 특별 가격에 넉넉한 유통기한과 과자 사은품까지 챙김.</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 3만 원 미만의 저렴한 가격으로 알찬 수량을 구매 가능함</t>
+          <t>편안한 소화감 — 지친 위장의 소화를 돕고 먹고 나면 확실하게 속이 편안해짐을 느낌.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>배송 중 해동 문제 — 배송 과정에서 제품이 전부 녹아 도착하는 경우가 있음</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3364,58 +3344,62 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>64,200원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260911094744_fdcb15f83b684390b6fd43416e90d400.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>898</v>
+        <v>56</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>속이 편안한 소화 지원 — 섭취 후 속이 편안해져 지속해서 먹기 좋음</t>
+          <t>부드러운 식감 — 일반 닭가슴살과 달리 퍽퍽함이 전혀 없고 쫄깃하고 부드러움.</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>맛있고 간편한 섭취 — 맛이 좋고 먹기 편해 자주 찾게 됨</t>
+          <t>다양하고 알찬 구성 — 스테이크, 소스 닭가슴살, 주먹밥 등 다채로운 구성을 질리지 않게 먹을 수 있음.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>저렴한 가격과 풍성한 사은품 — 착한 가격에 사은품 과자까지 제공되어 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>뛰어난 가성비 — 타 플랫폼에 비해 훨씬 많은 분량을 압도적으로 저렴한 가격에 구매함.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>아쉬운 배송 상태 — 냉동 제품임에도 배송 도중 다 녹아서 도착하여 보관하기 꺼려짐.</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
     </row>
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3423,58 +3407,58 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
+          <t>'1입 증정' 아일로 타입1 콜라겐 비오틴 앰플 14일분 오간자 에디션 + 앰플 1입 추가 증정</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>28,900원</t>
+          <t>32,900원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/4965673</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907090314_deefdfac70e6456194d7f4950eb47fcb.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>215</v>
+        <v>759</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>비리지 않은 달콤한 맛 — 단백질 음료 특유의 텁텁함과 비린 맛이 없어 먹기 좋음</t>
+          <t>고급스러운 패키지 — 선물 상자와 오간자 포장, 공주풍 케이스가 주는 시각적 만족도가 매우 큼.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>운동 후 단백질 보충 — 운동 후 깔끔하게 단백질을 채우기 좋고 가벼운 포만감을 줌</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>슬림한 용기의 높은 휴대성 — 패키지가 슬림하여 가방에 넣어 다니며 챙겨 마시기 편함</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>부담 없는 맛 — 새콤한 음료나 비타민을 마시는 듯한 맛으로 누구나 쉽게 즐길 수 있음.</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>호불호 갈리는 맛 — 일부 약이나 시럽 등을 섞어 둔 듯한 맛이 느껴져 약간 호불호가 갈림.</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3482,62 +3466,58 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>28,900원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14208051</t>
+          <t>https://gift.kakao.com/product/13550266</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260908134122_cb4724fa4d2d4e45b370faede2a463a5.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>102</v>
+        <v>215</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>고소한 베리말차 맛 — 말차 맛이 고소하여 거부감 없이 맛있게 섭취 가능함</t>
+          <t>텁텁함 없는 맛 — 특유의 비리고 텁텁한 맛이 전혀 없고 일반 초코/딸기 우유처럼 달콤함.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>더부룩함 해소 및 속 편안함 — 식후 복용 시 속이 편해지고 소화에 도움을 줌</t>
+          <t>높은 휴대성 — 팩 패키지 디자인이 매우 슬림하게 설계되어 가방에 넣고 다니며 먹기 편함.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>알찬 굿즈 및 사은품 구성 — 포토카드 및 단백질바 증정 등 가성비와 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>다소 느린 배송 속도 — 배송 진행이 다소 느린 편이라 아쉬움</t>
-        </is>
-      </c>
+          <t>확실한 포만감 — 운동 직후 섭취했을 때 가볍게 허기를 달래주고 포만감이 유지가 잘 됨.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
     <row r="18" ht="38" customHeight="1">
       <c r="B18" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3545,47 +3525,55 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>'1입 증정' 아일로 타입1 콜라겐 비오틴 앰플 14일분 오간자 에디션 + 앰플 1입 추가 증정</t>
+          <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>32,900원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965673</t>
+          <t>https://gift.kakao.com/product/14208051</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907090314_deefdfac70e6456194d7f4950eb47fcb.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260908134122_cb4724fa4d2d4e45b370faede2a463a5.jpg</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>759</v>
+        <v>102</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>고급스럽고 아름다운 포장 — 포장 상태가 고급스러우며 선물용으로 전달받았을 때 기분이 좋아짐</t>
+          <t>만족스러운 굿즈 구성 — 구매 시 리센느 멤버 원이의 포토카드와 단백질바 혜택이 제공되어 가성비가 훌륭함.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>새콤하고 맛있는 앰플 — 비타민 음료처럼 새콤달콤해서 거부감 없이 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>소화 기능 개선 — 식사 혹은 식단 조절 중 매일 속을 편안하게 조절해 주며 더부룩함을 완화함.</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>고소하고 맛있는 맛 — 효소 특유의 냄새 없이 고소하고 말차 특유의 향이 어우러져 맛있음.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>다소 지연된 배송 — 타 유통 채널 대비 배송 완료까지 시간이 다소 늦게 소요됨.</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
     </row>
@@ -3631,22 +3619,22 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>상큼하고 부담 없는 과일 맛 — 생강 성분 외에도 과일이 첨가되어 상큼하고 맛있게 마실 수 있음</t>
+          <t>귀여운 용기 디자인 — 미니보틀 패키지와 병의 크기가 너무 앙증맞고 예뻐 보관하기에 좋음.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>아침 활력 및 에너지 충전 — 공복에 마시면 활력이 생기고 기상 후 컨디션에 도움을 줌</t>
+          <t>부담 없는 생강 맛 — 생강 함량이 높음에도 과일 즙과 강황이 섞여 상큼한 과일주스처럼 먹기 수월함.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>귀여운 미니 보틀 디자인 — 병 디자인이 귀여워서 자주 손이 가고 기분 전환에 좋음</t>
+          <t>확실한 활력 효과 — 아침 비염이나 목 잠김 현상을 개선하고 공복 상태에서 몸을 깨우는 활력이 느껴짐.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>생강 맛에 대한 호불호 — 생강 특유의 알싸한 맛으로 인해 사람에 따라 거부감이 있을 수 있음</t>
+          <t>맵고 톡 쏘는 맛 — 생강의 매운 향과 톡 쏘는 특유의 잔향 때문에 아이나 입문자에게는 자극적임.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -3694,17 +3682,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>고함량 활력 및 피로 개선 — 6,200mg 고함량이라 섭취 후 활력이 넘치고 운동 지구력에 도움 됨</t>
+          <t>우수한 피로 해소 — 초고함량 아르기닌 설계로 운동이나 일상생활 시 뛰어난 집중력과 지구력을 보임.</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>개별 포장의 섭취 편의성 — 하루 한 포씩 개별 포장되어 휴대하고 복용하기 편함</t>
+          <t>편리한 섭취 및 휴대 — 하루 한 포만 뜯어서 섭취하면 되고 크기가 작아 보관 및 휴대가 간편함.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>고급스러운 선물 패키지 — 블랙/레드 패키지와 추가 증정 및 전용 쇼핑백 구성이 훌륭함</t>
+          <t>세련된 선물 포장 — 강렬하고 트렌디한 패키지와 전용 쇼핑백을 포함하여 선물 가치를 높임.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3722,51 +3710,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>BEST 프로틴모음 [랩노쉬] 프로틴 락커 12종 선물세트 (프로틴 드링크 퍼펙트, 단백쿠키, 단백 쿠키바)</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>랩노쉬</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12052312</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260723171929_09161ef5007a47039ea2ea7988556deb.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>다양한 베스트 모음 구성 — 다양한 제품과 맛을 한 번에 체험할 수 있는 알찬 구성임</t>
+          <t>뛰어난 숙취 해소 — 술자리 전후 복용 시 가벼운 기상을 돕고 다음 날 머리 무거움과 피로가 덜함.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>단백질 제품의 훌륭한 맛 — 일반 간식처럼 달콤하고 맛있게 즐길 수 있음</t>
+          <t>간편한 휴대성 — 슬림한 개별 포장 스틱 타입으로 물 없이 모임 자리나 술자리에 챙겨가기 좋음.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>고퀄리티 패키지 및 선물용 추천 — 포장이 푸짐하고 예뻐 선물 및 동호회 경품용으로 제격임</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>깔끔한 패키징 — 화장품을 연상케 하는 예쁜 보라색 세트 박스와 포장 쇼핑백으로 선물의 격을 올림.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>쌉싸름한 약재 맛 — 쌍화탕이나 한약 느낌의 쓴 맛과 약재 향이 있어 어린이 입맛에는 부담스러움.</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
     </row>
@@ -4100,7 +4092,7 @@
         <v>794</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>1677</v>
@@ -4109,7 +4101,7 @@
         <v>212</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>8723</v>
+        <v>8724</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>772</v>
@@ -4126,71 +4118,66 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 피로 회복 효과 — 섭취 후 피로 회복 및 활력 증진에 도움을 줌
-만족도 높은 선물 구성 — 받았을 때 기분이 좋고 주변과 나눠 먹기 좋은 선물임
-섭취 및 배송 편의성 — 마시기 편하고 배송 속도가 빠른 편임</t>
+          <t>뛰어난 피로회복 — 섭취 후 몸의 피로 회복과 활력 보충에 탁월한 효과를 느낌.
+만족스러운 선물 — 가성비는 낮지만 주고받을 때 서로 기분이 좋아져 선물용으로 매우 유용함.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>활력 및 피로 개선 — 섭취 시 활력이 도는 느낌을 받으며 피로 해소에 도움 됨
-고급스러운 선물 포장 — 포장이 고급스럽고 추가 증정 및 메시지 카드가 동봉되어 만족스러움
-빠른 배송 및 편의성 — 먹기 편하며 추석 연휴 전 빠르게 배송됨</t>
+          <t>활력 증진 효과 — 피곤할 때 섭취하면 몸에 빠르게 활력이 도는 느낌을 받음.
+고급스러운 포장 — 패키지가 고급스럽고 메시지 카드가 동봉되어 선물용으로 탁월함.
+편안한 섭취 방법 — 먹기에 부담이 없고 영양 성분 구성이 훌륭하여 챙겨 먹기 수월함.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>피로 감소 및 활력 증진 — 체력적으로 힘든 일할 때 마시면 생기와 활력이 느껴짐
-선물용 만족도 — 지인이나 가족에게 선물했을 때 기쁨과 만족도가 큼
-할인 쿠폰 구매 혜택 — 할인 쿠폰을 적용하여 좋은 가격에 구매 가능함</t>
+          <t>뛰어난 피로개선 — 고된 노동이나 활동 후 마시면 생기와 컨디션 회복에 큰 도움이 됨.
+선물용으로 추천 — 가족이나 지인에게 기분 좋게 마음을 전할 수 있는 정답 같은 선물임.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>활력 및 피로 회복 — 마시면 힘이 나고 피로할 때 도움을 줌
-개별 포장 및 휴대 편의성 — 한 포씩 개별 포장되어 가방이나 책상에 두고 챙겨 먹기 편함
-빠른 배송과 저렴한 가격 — 배송이 빠르고 저렴한 가격으로 구매할 수 있음</t>
+          <t>간편한 개별포장 — 한 포씩 개별 포장되어 사무실 책상이나 가방에 휴대하여 먹기 편함.
+우수한 피로회복 — 피로가 누적되었을 때 섭취하면 빠르게 힘이 나는 느낌을 줌.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>피로 개선 및 활력 충전 — 피곤할 때 섭취하기 좋고 활력이 상승하는 느낌을 줌
-선물하기 좋은 구성 — 포장이 깔끔하고 쇼핑백이 함께 들어있어 선물용으로 적합함
-넉넉한 용량과 높은 휴대성 — 양해 넉넉하고 여행 시 들고 다니며 챙겨 먹기 용이함</t>
+          <t>선물하기 좋은 구성 — 쇼핑백이 기본 동봉되고 포장이 정성스러워 선물용으로 안성맞춤임.
+휴대 및 섭취 용이 — 한 병씩 개별 용기로 되어 있어 여행 시 들고 다니며 챙겨 먹기 유용함.
+확실한 컨디션 개선 — 피로할 때 섭취 시 활력이 생겨 건강이 증진되는 효과를 직접 경험함.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 맛과 피로 회복 — 맛있고 피로가 빠르게 풀리는 효과를 기대할 수 있음
-고급스러운 포장 디자인 — 패키지가 고급스럽고 예쁘게 잘 되어 있어 선물하기 좋음
-개별 포장의 편의성 — 간편하게 개별 포장되어 있어 들고 다니며 먹기 편함</t>
+          <t>맛있는 액상형 — 영양제임에도 맛있게 복용할 수 있고 피로 해소가 빠른 편임.
+고급스러운 패키지 — 대기업 브랜드 제품답게 포장이 고급스러워 신뢰도 높은 선물로 제격임.
+편리한 개별포장 — 직장 등에서 간편하게 휴대하며 한 병씩 꺼내 먹기 용이함.</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>피로 회복 및 높은 섭취 편의성 — 피로감이 줄어들고 캡슐과 액상을 한 번에 먹기 편함
-알찬 구성 및 합리적 가격 — 30일 분량의 합리적인 가격대와 유용한 옵션 구성을 제공함</t>
+          <t>옵션 선택 다양성 — 옵션에서 취향에 맞는 맛이나 성분을 직접 고를 수 있어 만족스러움.
+정성스러운 포장 — 패키징이 매우 신경 써서 준비된 느낌을 주어 받는 사람의 기분이 좋아짐.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>에너지 충전 및 피로 개선 — 꾸준히 마시면 힘이 나고 피로가 해소되는 느낌을 받음
-상큼한 오렌지 맛 — 거부감 없이 맛있게 먹을 수 있는 오렌지 맛임
-예쁘고 정성스러운 포장 — 패키지가 예쁘고 꼼꼼하게 포장되어 전달됨</t>
+          <t>뛰어난 활력 증진 — 점심이나 힘든 일과 중 복용하면 즉각적으로 몸에 기운이 쌩쌩하게 돎.
+맛있는 오렌지맛 — 비타민 특유의 거부감 없이 맛있는 오렌지 맛으로 수월하게 먹을 수 있음.
+예쁜 패키지 포장 — 꼼꼼하고 화사하게 잘 포장되어 선물용으로 매우 만족스러움.</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>성별 맞춤 영양 설계 — 성별에 맞춰 선택할 수 있고 영양소 함량이 높음
-지속적인 효과 및 피로 개선 — 꾸준히 먹으면 덜 피곤하고 활력이 지속되는 효과를 느낌
-정성스러운 선물 포장 — 선물 느낌이 가득한 포장으로 전달받았을 때 만족도가 높음</t>
+          <t>맞춤형 옵션 선택 — 성별(m/f)에 맞춤 설계된 제품 옵션을 선택하여 선물할 수 있어 유용함.
+우수한 피로 개선 — 섭취 후 오랜 시간 피로감이 줄고 반짝이는 활력 효과가 오래 유지됨.</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 구미 형태 — 마이구미처럼 맛있어 영양제라는 부담 없이 먹기 좋음
-물 없이 먹는 편의성 — 젤리 제형이라 물 없이 간편하게 챙겨 먹기 유용함
-귀엽고 깔끔한 패키지 — 포장이 귀엽고 깔끔해 가볍게 선물하기 적합함</t>
+          <t>편리한 섭취 방식 — 물 없이도 출근길이나 야외에서 젤리처럼 가볍게 씹어서 먹을 수 있음.
+맛있는 구미 제형 — 영양제 냄새 없이 맛있는 마이구미 젤리 같아 남녀노소 즐기기 좋음.</t>
         </is>
       </c>
     </row>
@@ -4202,36 +4189,36 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>높은 가격 부담 — 영양제 가격대가 다소 비싸 부담스러움</t>
+          <t>부담스러운 가격 — 영양제의 효능은 만족스러우나 타 제품 대비 가격이 꽤 비싼 편임.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>쇼핑백 품질 불량 — 함께 전달된 쇼핑백 상태가 불량하여 선물하기 아쉬움</t>
+          <t>쇼핑백 품질 불량 — 함께 동봉된 선물용 백의 마감이나 상태가 불량하여 사용하기 어려웠음.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>배송 요청사항 미반영 — 관리실 위탁 요청에도 불구하고 문 앞에 두고 간 점이 아쉬움</t>
+          <t>배송 요청 미준수 — 부재 시 경비실 위탁을 사전 요청했으나 문 앞에 두고 가 아쉬웠음.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>야간 섭취 시 수면 방해 — 저녁 늦게 섭취 시 활력 성분으로 인해 잠들기 어려울 수 있음</t>
+          <t>수면 방해 가능성 — 피로회복 성분이 강하여 늦은 저녁에 복용 시 수면에 방해가 될 수 있음.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>배송 포장 오염 및 먼지 — 쇼핑백과 제품 박스 표면에 먼지 및 이물질이 가득 묻어옴
-개봉 씰 훼손 및 재부착 흔적 — 밀봉 스티커가 떼어져 있거나 재부착된 흔적이 있어 선물 시 찝찝함</t>
+          <t>비위생적 제품 상태 — 택배 상자 내부에 먼지나 이물질이 가득 묻은 상태로 배송되어 불쾌함.
+스티커 훼손 의심 — 박스 밀봉용 실 스티커가 반쯤 떨어져 있거나 재부착 흔적이 남아 찝찝함.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>다소 큰 알약 크기 — 기존 제품 대비 알약 크기가 커서 삼키기 다소 힘듦</t>
+          <t>큰 알약 크기 — 동봉된 알약의 크기가 기존 제품보다 큰 편이라 삼키는 데 다소 부담스러움.</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
@@ -4442,27 +4429,27 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -4499,29 +4486,29 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>아일로</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>셀렉스</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>셀렉스</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>아일로</t>
-        </is>
-      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
           <t>타이거모닝</t>
@@ -4534,7 +4521,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>랩노쉬</t>
+          <t>알디콤</t>
         </is>
       </c>
     </row>
@@ -4556,29 +4543,29 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
           <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
-        </is>
-      </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
+          <t>'1입 증정' 아일로 타입1 콜라겐 비오틴 앰플 14일분 오간자 에디션 + 앰플 1입 추가 증정</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
           <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>'1입 증정' 아일로 타입1 콜라겐 비오틴 앰플 14일분 오간자 에디션 + 앰플 1입 추가 증정</t>
-        </is>
-      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
           <t>[좋은 아침 선물] 진저샷 미니보틀 8개입 (메시지 참 증정)</t>
@@ -4591,7 +4578,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>BEST 프로틴모음 [랩노쉬] 프로틴 락커 12종 선물세트 (프로틴 드링크 퍼펙트, 단백쿠키, 단백 쿠키바)</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
     </row>
@@ -4645,19 +4632,19 @@
         <v>1679</v>
       </c>
       <c r="E19" s="3" t="n">
+        <v>898</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>898</v>
-      </c>
       <c r="G19" s="3" t="n">
+        <v>759</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>215</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="I19" s="3" t="n">
         <v>102</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>759</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>11</v>
@@ -4666,7 +4653,7 @@
         <v>248</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
@@ -4677,70 +4664,70 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 보자기 포장 — 보자기, 틴케이스 등 선물용으로 완성도 높은 포장을 제공함
-비리지 않고 뛰어난 맛 — 비린 맛이 전혀 없고 새콤하고 맛있게 섭취 가능함
-낱개 앰플의 간편함 — 낱개로 포장되어 하나씩 개봉해 먹기 편함</t>
+          <t>품격 있는 포장 — 오간자, 보자기, 고급 틴케이스 등 정성 가득하고 정밀한 패키지가 아름다움.
+비리지 않은 맛 — 콜라겐 특유의 텁텁하고 비린 맛이 느껴지지 않아 편하게 복용 가능함.
+간편한 앰플 형태 — 개별 앰플 제형으로 포장을 따서 즉시 마실 수 있어 관리가 간편함.</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>속 편한 소화 개선 효과 — 식후 섭취 시 소화가 잘 되고 속 불편함이 해소됨
-고소하고 부담 없는 맛 — 고소한 맛이 나며 거부감 없이 맛있게 섭취 가능함
-풍성한 사은품과 합리적 가격 — 단백질 바 등 사은품 혜택이 좋고 가격 대비 구성이 알참</t>
+          <t>뛰어난 소화 효과 — 식후에 섭취 시 속 더부룩함이 가라앉고 속이 매우 편안해짐.
+거부감 없는 맛 — 고소하고 군고구마 같은 맛이 나서 거부감 없이 쉽게 삼키기 좋음.
+풍성한 혜택 구성 — 라이브 방송 혜택 등으로 사은품과 증정품을 풍성하게 제공받음.</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>부드러운 식감과 다양한 맛 — 닭가슴살이 부드럽고 질리지 않는 다양한 맛으로 구성됨
-뛰어난 가성비 — 3만 원 미만의 저렴한 가격으로 알찬 수량을 구매 가능함</t>
+          <t>우수한 가성비 — 합리적이고 저렴한 특별 가격에 넉넉한 유통기한과 과자 사은품까지 챙김.
+편안한 소화감 — 지친 위장의 소화를 돕고 먹고 나면 확실하게 속이 편안해짐을 느낌.</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>속이 편안한 소화 지원 — 섭취 후 속이 편안해져 지속해서 먹기 좋음
-맛있고 간편한 섭취 — 맛이 좋고 먹기 편해 자주 찾게 됨
-저렴한 가격과 풍성한 사은품 — 착한 가격에 사은품 과자까지 제공되어 만족도가 높음</t>
+          <t>부드러운 식감 — 일반 닭가슴살과 달리 퍽퍽함이 전혀 없고 쫄깃하고 부드러움.
+다양하고 알찬 구성 — 스테이크, 소스 닭가슴살, 주먹밥 등 다채로운 구성을 질리지 않게 먹을 수 있음.
+뛰어난 가성비 — 타 플랫폼에 비해 훨씬 많은 분량을 압도적으로 저렴한 가격에 구매함.</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>비리지 않은 달콤한 맛 — 단백질 음료 특유의 텁텁함과 비린 맛이 없어 먹기 좋음
-운동 후 단백질 보충 — 운동 후 깔끔하게 단백질을 채우기 좋고 가벼운 포만감을 줌
-슬림한 용기의 높은 휴대성 — 패키지가 슬림하여 가방에 넣어 다니며 챙겨 마시기 편함</t>
+          <t>고급스러운 패키지 — 선물 상자와 오간자 포장, 공주풍 케이스가 주는 시각적 만족도가 매우 큼.
+부담 없는 맛 — 새콤한 음료나 비타민을 마시는 듯한 맛으로 누구나 쉽게 즐길 수 있음.</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>고소한 베리말차 맛 — 말차 맛이 고소하여 거부감 없이 맛있게 섭취 가능함
-더부룩함 해소 및 속 편안함 — 식후 복용 시 속이 편해지고 소화에 도움을 줌
-알찬 굿즈 및 사은품 구성 — 포토카드 및 단백질바 증정 등 가성비와 만족도가 높음</t>
+          <t>텁텁함 없는 맛 — 특유의 비리고 텁텁한 맛이 전혀 없고 일반 초코/딸기 우유처럼 달콤함.
+높은 휴대성 — 팩 패키지 디자인이 매우 슬림하게 설계되어 가방에 넣고 다니며 먹기 편함.
+확실한 포만감 — 운동 직후 섭취했을 때 가볍게 허기를 달래주고 포만감이 유지가 잘 됨.</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>고급스럽고 아름다운 포장 — 포장 상태가 고급스러우며 선물용으로 전달받았을 때 기분이 좋아짐
-새콤하고 맛있는 앰플 — 비타민 음료처럼 새콤달콤해서 거부감 없이 섭취 가능함</t>
+          <t>만족스러운 굿즈 구성 — 구매 시 리센느 멤버 원이의 포토카드와 단백질바 혜택이 제공되어 가성비가 훌륭함.
+소화 기능 개선 — 식사 혹은 식단 조절 중 매일 속을 편안하게 조절해 주며 더부룩함을 완화함.
+고소하고 맛있는 맛 — 효소 특유의 냄새 없이 고소하고 말차 특유의 향이 어우러져 맛있음.</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>상큼하고 부담 없는 과일 맛 — 생강 성분 외에도 과일이 첨가되어 상큼하고 맛있게 마실 수 있음
-아침 활력 및 에너지 충전 — 공복에 마시면 활력이 생기고 기상 후 컨디션에 도움을 줌
-귀여운 미니 보틀 디자인 — 병 디자인이 귀여워서 자주 손이 가고 기분 전환에 좋음</t>
+          <t>귀여운 용기 디자인 — 미니보틀 패키지와 병의 크기가 너무 앙증맞고 예뻐 보관하기에 좋음.
+부담 없는 생강 맛 — 생강 함량이 높음에도 과일 즙과 강황이 섞여 상큼한 과일주스처럼 먹기 수월함.
+확실한 활력 효과 — 아침 비염이나 목 잠김 현상을 개선하고 공복 상태에서 몸을 깨우는 활력이 느껴짐.</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>고함량 활력 및 피로 개선 — 6,200mg 고함량이라 섭취 후 활력이 넘치고 운동 지구력에 도움 됨
-개별 포장의 섭취 편의성 — 하루 한 포씩 개별 포장되어 휴대하고 복용하기 편함
-고급스러운 선물 패키지 — 블랙/레드 패키지와 추가 증정 및 전용 쇼핑백 구성이 훌륭함</t>
+          <t>우수한 피로 해소 — 초고함량 아르기닌 설계로 운동이나 일상생활 시 뛰어난 집중력과 지구력을 보임.
+편리한 섭취 및 휴대 — 하루 한 포만 뜯어서 섭취하면 되고 크기가 작아 보관 및 휴대가 간편함.
+세련된 선물 포장 — 강렬하고 트렌디한 패키지와 전용 쇼핑백을 포함하여 선물 가치를 높임.</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>다양한 베스트 모음 구성 — 다양한 제품과 맛을 한 번에 체험할 수 있는 알찬 구성임
-단백질 제품의 훌륭한 맛 — 일반 간식처럼 달콤하고 맛있게 즐길 수 있음
-고퀄리티 패키지 및 선물용 추천 — 포장이 푸짐하고 예뻐 선물 및 동호회 경품용으로 제격임</t>
+          <t>뛰어난 숙취 해소 — 술자리 전후 복용 시 가벼운 기상을 돕고 다음 날 머리 무거움과 피로가 덜함.
+간편한 휴대성 — 슬림한 개별 포장 스틱 타입으로 물 없이 모임 자리나 술자리에 챙겨가기 좋음.
+깔끔한 패키징 — 화장품을 연상케 하는 예쁜 보라색 세트 박스와 포장 쇼핑백으로 선물의 격을 올림.</t>
         </is>
       </c>
     </row>
@@ -4752,30 +4739,42 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>다소 높은 가격 부담 — 가격대가 다소 비싸고 점점 상승하는 경향이 있음</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>배송 중 해동 문제 — 배송 과정에서 제품이 전부 녹아 도착하는 경우가 있음</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>다소 느린 배송 속도 — 배송 진행이 다소 느린 편이라 아쉬움</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
+          <t>높은 가격대 — 원료가 좋으나 가격대가 제법 비싼 편이며 점차 가격이 올라 부담됨.</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>아쉬운 증정품 크기 — 함께 사은품으로 딸려 온 단백질칩 등의 사이즈가 매우 작아 실망스러움.</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>아쉬운 배송 상태 — 냉동 제품임에도 배송 도중 다 녹아서 도착하여 보관하기 꺼려짐.</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>호불호 갈리는 맛 — 일부 약이나 시럽 등을 섞어 둔 듯한 맛이 느껴져 약간 호불호가 갈림.</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>다소 지연된 배송 — 타 유통 채널 대비 배송 완료까지 시간이 다소 늦게 소요됨.</t>
+        </is>
+      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>생강 맛에 대한 호불호 — 생강 특유의 알싸한 맛으로 인해 사람에 따라 거부감이 있을 수 있음</t>
+          <t>맵고 톡 쏘는 맛 — 생강의 매운 향과 톡 쏘는 특유의 잔향 때문에 아이나 입문자에게는 자극적임.</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>쌉싸름한 약재 맛 — 쌍화탕이나 한약 느낌의 쓴 맛과 약재 향이 있어 어린이 입맛에는 부담스러움.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="1" t="inlineStr">
@@ -4795,29 +4794,29 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
+          <t>24,900원</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
           <t>64,200원</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>32,900원</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>28,900원</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>24,900원</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>28,900원</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>24,900원</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>32,900원</t>
-        </is>
-      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
           <t>29,900원</t>
@@ -4830,7 +4829,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5019,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5028,50 +5027,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 비눌린 워터믹스 10포</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,500원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953532&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/K8TCkwlN7kOaniMN8wZv994953532_00_00K8TCkwlN7kOaniMN8wZv.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>221</v>
+        <v>767</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>빠른 용해 및 쉬운 섭취 — 물에 금방 녹아 차 마시듯 편하게 마실 수 있음</t>
+          <t>뛰어난 활력 충전 — 피로 해소에 도움이 되며 특히 섭취 후 운동 시 에너지가 솟는 것을 느낌.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>개별 포장 및 휴대 편의성 — 스틱으로 개별 포장되어 외출 시 들고 다니기 편함</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>배변 활동 원활에 도움 — 하루 1포씩 복용 시 변비 개선에 효과가 느껴짐</t>
-        </is>
-      </c>
+          <t>거부감 없는 맛 — 비타500을 진하게 응축한 과일 맛이 나서 남녀노소 맛있게 먹을 수 있음.</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -5079,7 +5074,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5087,58 +5082,54 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 15포 15일분</t>
+          <t>LG생활건강 이너뷰 콜라겐 더마스틱 7포</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910891&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953528&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260312/tgDz0oHoOLB3gj3BLgFd610910891_00_01tgDz0oHoOLB3gj3BLgFd.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/9Cz26kBHEVc4QcQuToeY994953528_00_009Cz26kBHEVc4QcQuToeY.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>2205</v>
+        <v>513</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>간식 대용의 달콤한 맛 — 달달하여 식단 관리 중 간식 대용으로 먹기 좋음</t>
+          <t>넉넉한 제공량 — 타 유사 콜라겐 스틱 대비 함량이나 1포당 용량이 넉넉해 만족스러움.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>샐러드 섭취의 간편함 — 번거로운 샐러드 챙겨 먹기를 미니볼 형태로 간편히 대체 가능함</t>
+          <t>부담 없는 맛과 향 — 콜라겐 특유의 이상한 맛과 향의 거부감이 없고 상큼하고 편리하게 섭취 가능함.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>과도하게 딱딱한 제형 — 미니볼 제형이 너무 딱딱하여 씹을 때 치아에 부담을 줌</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5146,12 +5137,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>유한양행 초코맛 생유산균 스틱 20포 20일분</t>
+          <t>LG생활건강 이너뷰 히알루론산 더마스틱 12포</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5161,28 +5152,28 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651652&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953531&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260325/dj7lmBMZiAKAXlm5drGt600651652_00_00dj7lmBMZiAKAXlm5drGt.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/9sKzBlRNgLc6DDH1QsJU994953531_00_009sKzBlRNgLc6DDH1QsJU.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>451</v>
+        <v>468</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>진하고 맛있는 초코 향 — 초코 맛이 진해서 맛에 대한 거부감 없이 복용 가능함</t>
+          <t>간편한 개별 포장 — 한 포씩 소포장 설계가 되어 있어 외출 시 가방에 한 포씩 들고 다니며 위생적으로 먹기 좋음.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>합리적인 가격 및 편의성 — 가격대가 합리적이며 스틱 형태라 복용이 편함</t>
+          <t>맛있는 제품 제형 — 맛이 좋아 거부감이 없으며 일상생활 도중 간식처럼 섭취하기 훌륭함.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -5201,12 +5192,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 밀크씨슬 30정 30일분</t>
+          <t>[신혜선 PICK] 동국제약 마데카 글루타치온 필름 12매 12일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5216,35 +5207,43 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000134&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911099&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/bzKNvkJzwy2KdAqrXtDQ600000134_00_00bzKNvkJzwy2KdAqrXtDQ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260728/NbSqiy25P90IFlYxB3ux610911099_00_01NbSqiy25P90IFlYxB3ux.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3808</v>
+        <v>245</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>뛰어난 가성비와 성분 — 저렴한 가격임에도 알찬 성분을 갖추어 만족스러움</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>편리한 필름 제형 — 입천장에 붙여 간편하게 녹여 먹는 방식으로 핸드백 등에 간편 수납이 됨.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>우수한 가성비 — 고가의 글루타치온 제품을 다이소 채널을 통해 가성비 높게 체험해 볼 수 있음.</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>호불호 있는 맛 — 끝 맛이 미세하게 비리거나 당도가 높은 편이어서 깔끔한 맛을 선호하면 불만족스러움.</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5252,12 +5251,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 녹차카테킨 30정 30일분</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5267,43 +5266,47 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/qm625V7JKEa8Iu7GrFAf987253276_00_01qm625V7JKEa8Iu7GrFAf.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3663</v>
+        <v>665</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>체지방 관리 및 배변 원활 — 운동 및 식사 전후 복용 시 배변 활동이 원활해짐</t>
+          <t>운동 및 영양 보충 — 근력 운동 시 복용하면 안전하게 체력을 유지하고 단백질 보충을 돕기에 적당함.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>간편한 챙겨 먹기 — 하루 한 알씩 편리하게 챙겨 먹기 좋음</t>
+          <t>무난한 무맛 제형 — 특별하게 호불호가 갈릴 수 있는 이상한 향이나 맛이 전혀 나지 않아 편리함.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>다소 큰 알약 크기 — 알약의 크기가 커서 삼킬 때 부담스러울 수 있음</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+          <t>불편한 가루 타입 — 완전한 가루 타입으로 구성되어 별도 섭취나 개량 시 약간 흩날려 번거로움.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>살짝 느끼한 맛 — 복용 시 개인 체감에 따라 다소 맛이 밋밋하거나 텁텁하고 느끼하게 느껴짐.</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5311,12 +5314,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>동국제약 비타민D 2000IU 40캡슐 40일분</t>
+          <t>동화 부채표 편안활 5포 5일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5326,35 +5329,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910777&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618636&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251229/5qFLremik89lsUa72Yqy610910777_00_005qFLremik89lsUa72Yqy.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260414/Rr7eEkWvVmX4lCcRcfuW601618636_00_00Rr7eEkWvVmX4lCcRcfuW.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1135</v>
+        <v>3417</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>작은 알약 크기와 목넘김 — 알약 크기가 작아 목넘김이 매우 편함</t>
+          <t>편리한 휴대 및 상비 — 낱개 포장으로 휴대가 쉽고 속이 더부룩할 때 대비하여 비상용 상비약으로 구비하기 유용함.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>캡슐형의 낮은 거부감 — 가루 제형과 달리 신맛 없이 부드럽게 복용 가능함</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>높은 가성비 — 저렴한 가격으로 꾸준히 부담 없이 구매하기 좋음</t>
-        </is>
-      </c>
+          <t>뛰어난 소화 효과 — 소량 섭취만으로도 기존 액상 소화제와 유사하게 체한 속을 빠르게 내려 줌.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -5362,7 +5361,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5370,12 +5369,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
+          <t>[신혜선 PICK] 동국제약 마데카 PDRN 필름 10매 10일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -5385,43 +5384,43 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911098&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260422/qm625V7JKEa8Iu7GrFAf987253276_00_01qm625V7JKEa8Iu7GrFAf.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260728/2LpWqYu8CZWzex7rdnk8610911098_00_012LpWqYu8CZWzex7rdnk8.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>664</v>
+        <v>88</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>운동 및 단백질 보충 적합성 — 건강하게 운동할 때 복용하거나 단백질 보충용으로 적합함</t>
+          <t>뛰어난 휴대 편의성 — 매우 가볍고 얇은 미니 사이즈 필름으로 화장품 파우치 속에 수납하여 챙기기 좋음.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>부담 없는 무맛 — 자극적인 맛이나 향이 없어 부담 없이 복용 가능함</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>가루 제형의 불편함 — 분말 타입이라 가루를 섭취하기 다소 번거로울 수 있음</t>
-        </is>
-      </c>
+          <t>상큼하고 맛있는 맛 — 새콤달콤한 맛이라 물 없이 간식처럼 간편하고 맛있게 먹기 편리함.</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>합리적인 판매 가격 — 저렴한 단가로 체험해 보고 대량 구매 전에 자가 테스트용으로 구매하기 좋음.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5429,54 +5428,58 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 아르기닌 구미 7일분</t>
+          <t>[신혜선 PICK] 동국제약 프로폴리스＆아연 필름 12매 12일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306206&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911097&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260417/GhOqeQ2jNHaIvb2k8Oj6032306206_00_01GhOqeQ2jNHaIvb2k8Oj6.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260805/WQN2sdlFQlgUeYP1OzCA610911097_00_01WQN2sdlFQlgUeYP1OzCA.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>578</v>
+        <v>59</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>맛있는 젤리 구미 형태 — 구미 형태라 맛이 좋고 거부감 없이 먹을 수 있음</t>
+          <t>높은 섭취 편의성 — 물 없이 즉석에서 천천히 입안에 붙여 녹이는 방식으로 복용 프로세스가 매우 간단함.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1주일 단위 간편 포장 — 하루에 하나씩 일주일 동안 먹을 수 있도록 구성되어 편함</t>
+          <t>편리한 보관과 휴대 — 매우 슬림하여 주머니나 가방에 휴대하고 다니다가 목 건강이 염려될 때 먹기 수월함.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>다소 쓴 약재 맛 — 아연과 프로폴리스의 농도가 짙어 사람에 따라 한약같이 다소 쓰게 느껴짐.</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5484,12 +5487,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>자연관 홍삼정 에너타임 망고맛 14포 14일분</t>
+          <t>홀베리 유기농 레몬즙 10포</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5499,36 +5502,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762104&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923434&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260612/M1nlLjjHeflYgIz5zIxp901762104_00_01M1nlLjjHeflYgIz5zIxp.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260305/6AQS4j3WbfucTbhmJ4ur965923434_00_006AQS4j3WbfucTbhmJ4ur.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>55</v>
+        <v>1588</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>망고 맛의 부담 없는 풍미 — 망고 향이 홍삼 특유의 맛을 중화시켜 맛있게 먹기 좋음</t>
+          <t>상큼하고 맛있는 맛 — 물이나 시원한 음료에 타서 먹을 수 있는 신선하고 매우 상큼한 맛을 보유함.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>개별 포장의 높은 휴대성 — 개별 스틱 포장으로 휴대 및 간편 섭취에 유용함</t>
+          <t>우수한 가성비 — 시중 가품 우려 없이 합리적이고 신뢰도 높은 유기농 레몬즙을 안심하고 구매 가능함.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>높은 당 함량 및 재고 부족 — 당류 함량이 다소 높고 품절이 자주 발생함</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -5543,7 +5542,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 마데카 글루타치온 필름 12매 12일분</t>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5553,39 +5552,39 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911099&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911102&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260728/NbSqiy25P90IFlYxB3ux610911099_00_01NbSqiy25P90IFlYxB3ux.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/D3MtLfS4wvzyyoiG4ppT610911102_00_01D3MtLfS4wvzyyoiG4ppT.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J11" t="n">
-        <v>245</v>
+        <v>89</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>구강 용해 필름의 편의성 — 입천장에 붙여 먹는 필름 형태로 휴대와 복용이 간편함</t>
+          <t>뛰어난 구강 청량감 — 입에 넣고 씹는 순간 캡슐이 터지며 시원한 레몬 민트의 민트 향이 싹 퍼짐.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>부담 없는 가성비 — 저렴한 가격으로 글루타치온 제품을 체험하기 적합함</t>
+          <t>뛰어난 응급 대용성 — 외출 시 양치를 하기 애매하거나 매너가 필요한 미팅 전에 긴급히 해결 가능함.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>호불호 갈리는 비린 맛 — 맛이 다소 단 편이고 특유의 비린 향이 느껴질 수 있음</t>
+          <t>불편한 캡슐 껍질 — 액상이 터진 이후 외피 잔여 껍질이 입안에 남아 이물감이 느껴질 수 있음.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -5702,47 +5701,47 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5759,47 +5758,47 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>이너뷰 바이 리튠</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>이너뷰 바이 리튠</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>유한양행</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
+          <t>동화약품</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>익스트림</t>
-        </is>
-      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5816,52 +5815,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 비눌린 워터믹스 10포</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 15포 15일분</t>
+          <t>LG생활건강 이너뷰 콜라겐 더마스틱 7포</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>유한양행 초코맛 생유산균 스틱 20포 20일분</t>
+          <t>LG생활건강 이너뷰 히알루론산 더마스틱 12포</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 밀크씨슬 30정 30일분</t>
+          <t>[신혜선 PICK] 동국제약 마데카 글루타치온 필름 12매 12일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 녹차카테킨 30정 30일분</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>동국제약 비타민D 2000IU 40캡슐 40일분</t>
+          <t>동화 부채표 편안활 5포 5일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
+          <t>[신혜선 PICK] 동국제약 마데카 PDRN 필름 10매 10일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 아르기닌 구미 7일분</t>
+          <t>[신혜선 PICK] 동국제약 프로폴리스＆아연 필름 12매 12일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>자연관 홍삼정 에너타임 망고맛 14포 14일분</t>
+          <t>홀베리 유기농 레몬즙 10포</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 마데카 글루타치온 필름 12매 12일분</t>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
     </row>
@@ -5872,34 +5871,34 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>4.7</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>4.8</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>4.7</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="7">
@@ -5909,34 +5908,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>221</v>
+        <v>767</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2205</v>
+        <v>513</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>451</v>
+        <v>468</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3808</v>
+        <v>245</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>3663</v>
+        <v>665</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1135</v>
+        <v>3417</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>664</v>
+        <v>88</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>578</v>
+        <v>59</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>55</v>
+        <v>1588</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>245</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -5947,100 +5946,97 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>빠른 용해 및 쉬운 섭취 — 물에 금방 녹아 차 마시듯 편하게 마실 수 있음
-개별 포장 및 휴대 편의성 — 스틱으로 개별 포장되어 외출 시 들고 다니기 편함
-배변 활동 원활에 도움 — 하루 1포씩 복용 시 변비 개선에 효과가 느껴짐</t>
+          <t>뛰어난 활력 충전 — 피로 해소에 도움이 되며 특히 섭취 후 운동 시 에너지가 솟는 것을 느낌.
+거부감 없는 맛 — 비타500을 진하게 응축한 과일 맛이 나서 남녀노소 맛있게 먹을 수 있음.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>간식 대용의 달콤한 맛 — 달달하여 식단 관리 중 간식 대용으로 먹기 좋음
-샐러드 섭취의 간편함 — 번거로운 샐러드 챙겨 먹기를 미니볼 형태로 간편히 대체 가능함</t>
+          <t>넉넉한 제공량 — 타 유사 콜라겐 스틱 대비 함량이나 1포당 용량이 넉넉해 만족스러움.
+부담 없는 맛과 향 — 콜라겐 특유의 이상한 맛과 향의 거부감이 없고 상큼하고 편리하게 섭취 가능함.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>진하고 맛있는 초코 향 — 초코 맛이 진해서 맛에 대한 거부감 없이 복용 가능함
-합리적인 가격 및 편의성 — 가격대가 합리적이며 스틱 형태라 복용이 편함</t>
+          <t>간편한 개별 포장 — 한 포씩 소포장 설계가 되어 있어 외출 시 가방에 한 포씩 들고 다니며 위생적으로 먹기 좋음.
+맛있는 제품 제형 — 맛이 좋아 거부감이 없으며 일상생활 도중 간식처럼 섭취하기 훌륭함.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가성비와 성분 — 저렴한 가격임에도 알찬 성분을 갖추어 만족스러움</t>
+          <t>편리한 필름 제형 — 입천장에 붙여 간편하게 녹여 먹는 방식으로 핸드백 등에 간편 수납이 됨.
+우수한 가성비 — 고가의 글루타치온 제품을 다이소 채널을 통해 가성비 높게 체험해 볼 수 있음.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>체지방 관리 및 배변 원활 — 운동 및 식사 전후 복용 시 배변 활동이 원활해짐
-간편한 챙겨 먹기 — 하루 한 알씩 편리하게 챙겨 먹기 좋음</t>
+          <t>운동 및 영양 보충 — 근력 운동 시 복용하면 안전하게 체력을 유지하고 단백질 보충을 돕기에 적당함.
+무난한 무맛 제형 — 특별하게 호불호가 갈릴 수 있는 이상한 향이나 맛이 전혀 나지 않아 편리함.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>작은 알약 크기와 목넘김 — 알약 크기가 작아 목넘김이 매우 편함
-캡슐형의 낮은 거부감 — 가루 제형과 달리 신맛 없이 부드럽게 복용 가능함
-높은 가성비 — 저렴한 가격으로 꾸준히 부담 없이 구매하기 좋음</t>
+          <t>편리한 휴대 및 상비 — 낱개 포장으로 휴대가 쉽고 속이 더부룩할 때 대비하여 비상용 상비약으로 구비하기 유용함.
+뛰어난 소화 효과 — 소량 섭취만으로도 기존 액상 소화제와 유사하게 체한 속을 빠르게 내려 줌.</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>운동 및 단백질 보충 적합성 — 건강하게 운동할 때 복용하거나 단백질 보충용으로 적합함
-부담 없는 무맛 — 자극적인 맛이나 향이 없어 부담 없이 복용 가능함</t>
+          <t>뛰어난 휴대 편의성 — 매우 가볍고 얇은 미니 사이즈 필름으로 화장품 파우치 속에 수납하여 챙기기 좋음.
+상큼하고 맛있는 맛 — 새콤달콤한 맛이라 물 없이 간식처럼 간편하고 맛있게 먹기 편리함.
+합리적인 판매 가격 — 저렴한 단가로 체험해 보고 대량 구매 전에 자가 테스트용으로 구매하기 좋음.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 젤리 구미 형태 — 구미 형태라 맛이 좋고 거부감 없이 먹을 수 있음
-1주일 단위 간편 포장 — 하루에 하나씩 일주일 동안 먹을 수 있도록 구성되어 편함</t>
+          <t>높은 섭취 편의성 — 물 없이 즉석에서 천천히 입안에 붙여 녹이는 방식으로 복용 프로세스가 매우 간단함.
+편리한 보관과 휴대 — 매우 슬림하여 주머니나 가방에 휴대하고 다니다가 목 건강이 염려될 때 먹기 수월함.</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>망고 맛의 부담 없는 풍미 — 망고 향이 홍삼 특유의 맛을 중화시켜 맛있게 먹기 좋음
-개별 포장의 높은 휴대성 — 개별 스틱 포장으로 휴대 및 간편 섭취에 유용함</t>
+          <t>상큼하고 맛있는 맛 — 물이나 시원한 음료에 타서 먹을 수 있는 신선하고 매우 상큼한 맛을 보유함.
+우수한 가성비 — 시중 가품 우려 없이 합리적이고 신뢰도 높은 유기농 레몬즙을 안심하고 구매 가능함.</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>구강 용해 필름의 편의성 — 입천장에 붙여 먹는 필름 형태로 휴대와 복용이 간편함
-부담 없는 가성비 — 저렴한 가격으로 글루타치온 제품을 체험하기 적합함</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>뛰어난 구강 청량감 — 입에 넣고 씹는 순간 캡슐이 터지며 시원한 레몬 민트의 민트 향이 싹 퍼짐.
+뛰어난 응급 대용성 — 외출 시 양치를 하기 애매하거나 매너가 필요한 미팅 전에 긴급히 해결 가능함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>과도하게 딱딱한 제형 — 미니볼 제형이 너무 딱딱하여 씹을 때 치아에 부담을 줌</t>
-        </is>
-      </c>
+      <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>호불호 있는 맛 — 끝 맛이 미세하게 비리거나 당도가 높은 편이어서 깔끔한 맛을 선호하면 불만족스러움.</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>다소 큰 알약 크기 — 알약의 크기가 커서 삼킬 때 부담스러울 수 있음</t>
+          <t>불편한 가루 타입 — 완전한 가루 타입으로 구성되어 별도 섭취나 개량 시 약간 흩날려 번거로움.
+살짝 느끼한 맛 — 복용 시 개인 체감에 따라 다소 맛이 밋밋하거나 텁텁하고 느끼하게 느껴짐.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>가루 제형의 불편함 — 분말 타입이라 가루를 섭취하기 다소 번거로울 수 있음</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>높은 당 함량 및 재고 부족 — 당류 함량이 다소 높고 품절이 자주 발생함</t>
-        </is>
-      </c>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>다소 쓴 약재 맛 — 아연과 프로폴리스의 농도가 짙어 사람에 따라 한약같이 다소 쓰게 느껴짐.</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>호불호 갈리는 비린 맛 — 맛이 다소 단 편이고 특유의 비린 향이 느껴질 수 있음</t>
+          <t>불편한 캡슐 껍질 — 액상이 터진 이후 외피 잔여 껍질이 입안에 남아 이물감이 느껴질 수 있음.</t>
         </is>
       </c>
     </row>
@@ -6052,52 +6048,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>1,500원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>1,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
         </is>
       </c>
     </row>
@@ -6284,27 +6280,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
+          <t>[1일 1정] 바이탈뷰티 메타그린 슬림업 30일</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>빌드</t>
+          <t>바이탈뷰티</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000219379&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000248462&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021937922ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024846232ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -6370,27 +6366,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>빌드</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000219379&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021937922ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -6405,7 +6401,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6413,27 +6409,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18,800원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364589ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -6456,7 +6452,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>고려은단 비타민C1000 120정 (4개월분)</t>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (60일분)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -6466,17 +6462,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>12,900원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000002944&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000164736&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0000/A00000000294413ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0016/A00000016473623ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -6499,27 +6495,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>39,800원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -6534,7 +6530,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6542,27 +6538,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31,900원</t>
+          <t>13,950원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014345ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -6577,7 +6573,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6585,46 +6581,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>정관장 활기력 20ml*16병 (16일분)</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>정관장</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>41,400원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000129374&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0012/A00000012937405ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>204</v>
+        <v>25395</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>컨디션 회복 및 피로 관리 — 몸이 피로하거나 컨디션이 저하될 때 챙겨 먹기 좋음</t>
+          <t>탁월한 목 넘김 — 초미세 크기의 초경량 캡슐로 설계되어 한 입에 털어 넣어도 부드럽게 넘어감.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>높은 선물 가치 — 유명 브랜드 제품으로 선물받았을 때 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>질과 장 동시 케어 — 여성들의 민감한 질 유해균 억제와 장 활성화를 더블케어로 효율 좋게 보살핌.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>귀여운 콜라보 굿즈 — 포켓몬 에디션 카드케이스 등 희소하고 앙증맞은 랜덤 수집형 굿즈를 제공함.</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -6632,7 +6632,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6640,50 +6640,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[호빵맨콜라보] 이너플로라 질유산균 60캡슐+호빵맨 스티커 / 이노시톨콜린 30포</t>
+          <t>세노비스 피부촉촉 히알루론산 10개입 (10일분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>뉴오리진</t>
+          <t>세노비스</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>39,900원</t>
+          <t>14,200원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247265&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000146479&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024726512ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0014/A00000014647912ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>5189</v>
+        <v>4945</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>질 및 장 건강 개선 — 꾸준히 복용 시 분비물이나 냉 개선에 효과적임</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>목넘김이 쉬운 미니 알약 — 알약의 크기가 매우 작아 목넘김과 삼키기가 쉬움</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>귀여운 콜라보 증정 구성 — 호빵맨 캐릭터 콜라보 패키지와 스티커 구성이 귀여움</t>
-        </is>
-      </c>
+          <t>추천 이너뷰티 템 — 피부 수분과 다이어트 이너케어를 겸하며 다른 간식들과 식단 관리용으로 먹기 좋음.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -6699,50 +6691,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>씨제이웰케어</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,900원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>18648</v>
+        <v>15367</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>압도적인 가성비 — 타사 대비 가격이 저렴해 장기 복용에 부담이 없음</t>
+          <t>뛰어난 입면 효과 — 복용 후 단시간 내에 자연스럽게 깊은 잠을 유도해 숙면할 수 있도록 조율함.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>개별 포장 및 휴대 편의성 — 개별 포장으로 위생적이고 외출 시 들고 다니기 간편함</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>간편한 기초 영양 관리 — 한 알로 다양한 비타민과 미네랄을 한 번에 챙기기 좋음</t>
-        </is>
-      </c>
+          <t>편안한 젤리 타입 — 부담스럽고 위장에 머무는 알약이 아닌 새콤하고 쫄깃한 구미라 자기 전 먹기 수월함.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -6873,32 +6861,32 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
-        </is>
-      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -6915,52 +6903,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>바이탈뷰티</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>딥트3일</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>빌드</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>딥트3일</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>바이오코어유산균</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>세노비스</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>멜라메이트</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>푸드올로지</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>고려은단</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>푸드올로지</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>정관장</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>뉴오리진</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>씨제이웰케어</t>
         </is>
       </c>
     </row>
@@ -6972,52 +6960,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>[1일 1정] 바이탈뷰티 메타그린 슬림업 30일</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (60일분)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>세노비스 피부촉촉 히알루론산 10개입 (10일분)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>고려은단 비타민C1000 120정 (4개월분)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>정관장 활기력 20ml*16병 (16일분)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[호빵맨콜라보] 이너플로라 질유산균 60캡슐+호빵맨 스티커 / 이노시톨콜린 30포</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
         </is>
       </c>
     </row>
@@ -7035,10 +7023,10 @@
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>4.8</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>4.9</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.8</v>
@@ -7058,13 +7046,13 @@
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="n">
-        <v>204</v>
+        <v>25395</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>5189</v>
+        <v>4945</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>18648</v>
+        <v>15367</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -7082,22 +7070,20 @@
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>컨디션 회복 및 피로 관리 — 몸이 피로하거나 컨디션이 저하될 때 챙겨 먹기 좋음
-높은 선물 가치 — 유명 브랜드 제품으로 선물받았을 때 만족도가 높음</t>
+          <t>탁월한 목 넘김 — 초미세 크기의 초경량 캡슐로 설계되어 한 입에 털어 넣어도 부드럽게 넘어감.
+질과 장 동시 케어 — 여성들의 민감한 질 유해균 억제와 장 활성화를 더블케어로 효율 좋게 보살핌.
+귀여운 콜라보 굿즈 — 포켓몬 에디션 카드케이스 등 희소하고 앙증맞은 랜덤 수집형 굿즈를 제공함.</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>질 및 장 건강 개선 — 꾸준히 복용 시 분비물이나 냉 개선에 효과적임
-목넘김이 쉬운 미니 알약 — 알약의 크기가 매우 작아 목넘김과 삼키기가 쉬움
-귀여운 콜라보 증정 구성 — 호빵맨 캐릭터 콜라보 패키지와 스티커 구성이 귀여움</t>
+          <t>추천 이너뷰티 템 — 피부 수분과 다이어트 이너케어를 겸하며 다른 간식들과 식단 관리용으로 먹기 좋음.</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>압도적인 가성비 — 타사 대비 가격이 저렴해 장기 복용에 부담이 없음
-개별 포장 및 휴대 편의성 — 개별 포장으로 위생적이고 외출 시 들고 다니기 간편함
-간편한 기초 영양 관리 — 한 알로 다양한 비타민과 미네랄을 한 번에 챙기기 좋음</t>
+          <t>뛰어난 입면 효과 — 복용 후 단시간 내에 자연스럽게 깊은 잠을 유도해 숙면할 수 있도록 조율함.
+편안한 젤리 타입 — 부담스럽고 위장에 머무는 알약이 아닌 새콤하고 쫄깃한 구미라 자기 전 먹기 수월함.</t>
         </is>
       </c>
     </row>
@@ -7126,52 +7112,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>24,900원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>16,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>18,900원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>16,000원</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>31,900원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>10,900원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>39,800원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>13,950원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>14,200원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>16,900원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>18,800원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>12,900원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>17,900원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>31,900원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>41,400원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>39,900원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>5,900원</t>
         </is>
       </c>
     </row>
@@ -7259,7 +7245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7301,16 +7287,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>37.5</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
         <v>4</v>
@@ -7363,61 +7349,61 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
         <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -7446,28 +7432,6 @@
       </c>
       <c r="F8" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>비타민D</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
